--- a/자리배치표.xlsx
+++ b/자리배치표.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -497,34 +497,34 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>이민재</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>이옥순</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>김미정</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>신지아</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>최정남</t>
-        </is>
-      </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>오지아</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>김정호</t>
+          <t>장민지</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>권영숙</t>
+          <t>노상현</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
@@ -534,94 +534,17 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
+          <t>노상현</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>이옥순</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
           <t>장민지</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>최시우</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>김도윤</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>김경수</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>노상현</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>김하은</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>오명자</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>김준호</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>최준혁</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>김미정</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>김민재</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>박경수</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>최상현</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>박지민</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>박현주</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>이옥순</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>백채원</t>
         </is>
       </c>
     </row>
@@ -636,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -649,7 +572,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>백채원</t>
+          <t>장민지</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -657,166 +580,89 @@
           <t>이옥순</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>노상현</t>
+        </is>
+      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>박현주</t>
+          <t>이민재</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>박지민</t>
+          <t>노상현</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>최상현</t>
+          <t>장민지</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>박경수</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>김민재</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>김미정</t>
+          <t>이옥순</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>최준혁</t>
+          <t>이민재</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>김준호</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>오명자</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>김하은</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>노상현</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>김경수</t>
-        </is>
-      </c>
+      <c r="A3" s="1" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>김도윤</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>최시우</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>장민지</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>이민재</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>권영숙</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>김정호</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>오지아</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>최정남</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>신지아</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>김미정</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
-      <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr"/>
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
